--- a/appointment_forms/035_home_organization_service_request--appointment_forms.xlsx
+++ b/appointment_forms/035_home_organization_service_request--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -877,12 +877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -900,12 +900,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>home_type</t>
+          <t>home_type_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Home Type</t>
+          <t>Home Type 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -923,12 +923,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>service_type</t>
+          <t>service_type_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Service Type</t>
+          <t>Service Type 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -946,12 +946,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>service_request</t>
+          <t>service_request_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Service Request</t>
+          <t>Service Request 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>followup</t>
+          <t>followup_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Followup</t>
+          <t>Followup 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1287,233 +1287,165 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>followup_choices</t>
+          <t>home_type_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>followup_choices</t>
+          <t>home_type_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>home_type_choices</t>
+          <t>home_type_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>triplex</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Triplex</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>home_type_choices</t>
+          <t>service_type_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>double</t>
+          <t>organizing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Double</t>
+          <t>Organizing</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>home_type_choices</t>
+          <t>service_type_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>triplex</t>
+          <t>cleaning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Triplex</t>
+          <t>Cleaning</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>service_type_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>organizing</t>
+          <t>packing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Organizing</t>
+          <t>Packing</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>followup_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cleaning</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleaning</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>service_type_choices</t>
+          <t>followup_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>packing</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Packing</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>followup_choices</t>
+          <t>followup_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>followup_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>followup_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>followup_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>followup_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
